--- a/data/ams_weekly_data/Audio_Array/ads_report_week19.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week19.xlsx
@@ -12987,7 +12987,7 @@
         <v>8563.280000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>7.666666666666667</v>
+        <v>8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>8563.280000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>7.666666666666667</v>
+        <v>8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>8563.280000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>7.666666666666667</v>
+        <v>8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26682.66666666667</v>
+        <v>26683</v>
       </c>
       <c r="E13" t="n">
-        <v>135.6666666666667</v>
+        <v>136</v>
       </c>
       <c r="F13" t="n">
         <v>2070.17</v>
@@ -13185,7 +13185,7 @@
         <v>15831.64</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -13206,10 +13206,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>26682.66666666667</v>
+        <v>26683</v>
       </c>
       <c r="E14" t="n">
-        <v>135.6666666666667</v>
+        <v>136</v>
       </c>
       <c r="F14" t="n">
         <v>2070.17</v>
@@ -13218,7 +13218,7 @@
         <v>15831.64</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -13239,10 +13239,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26682.66666666667</v>
+        <v>26683</v>
       </c>
       <c r="E15" t="n">
-        <v>135.6666666666667</v>
+        <v>136</v>
       </c>
       <c r="F15" t="n">
         <v>2070.17</v>
@@ -13251,7 +13251,7 @@
         <v>15831.64</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -13272,10 +13272,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E16" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F16" t="n">
         <v>484.0067857142857</v>
@@ -13284,7 +13284,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -13305,10 +13305,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E17" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F17" t="n">
         <v>484.0067857142857</v>
@@ -13317,7 +13317,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -13338,10 +13338,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E18" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F18" t="n">
         <v>484.0067857142857</v>
@@ -13350,7 +13350,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -13371,10 +13371,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E19" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
         <v>484.0067857142857</v>
@@ -13383,7 +13383,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E20" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F20" t="n">
         <v>484.0067857142857</v>
@@ -13416,7 +13416,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -13437,10 +13437,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E21" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F21" t="n">
         <v>484.0067857142857</v>
@@ -13449,7 +13449,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E22" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F22" t="n">
         <v>484.0067857142857</v>
@@ -13482,7 +13482,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -13503,10 +13503,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E23" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
         <v>484.0067857142857</v>
@@ -13515,7 +13515,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -13536,10 +13536,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E24" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
         <v>484.0067857142857</v>
@@ -13548,7 +13548,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -13569,10 +13569,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E25" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
         <v>484.0067857142857</v>
@@ -13581,7 +13581,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -13602,10 +13602,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E26" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F26" t="n">
         <v>484.0067857142857</v>
@@ -13614,7 +13614,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E27" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F27" t="n">
         <v>484.0067857142857</v>
@@ -13647,7 +13647,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -13668,10 +13668,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E28" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F28" t="n">
         <v>484.0067857142857</v>
@@ -13680,7 +13680,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -13701,10 +13701,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E29" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F29" t="n">
         <v>484.0067857142857</v>
@@ -13713,7 +13713,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -13734,10 +13734,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E30" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F30" t="n">
         <v>484.0067857142857</v>
@@ -13746,7 +13746,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -13767,10 +13767,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E31" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F31" t="n">
         <v>484.0067857142857</v>
@@ -13779,7 +13779,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -13800,10 +13800,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E32" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F32" t="n">
         <v>484.0067857142857</v>
@@ -13812,7 +13812,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -13833,10 +13833,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E33" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F33" t="n">
         <v>484.0067857142857</v>
@@ -13845,7 +13845,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -13866,10 +13866,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E34" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F34" t="n">
         <v>484.0067857142857</v>
@@ -13878,7 +13878,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -13899,10 +13899,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E35" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F35" t="n">
         <v>484.0067857142857</v>
@@ -13911,7 +13911,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E36" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F36" t="n">
         <v>484.0067857142857</v>
@@ -13944,7 +13944,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -13965,10 +13965,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E37" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F37" t="n">
         <v>484.0067857142857</v>
@@ -13977,7 +13977,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -13998,10 +13998,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E38" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F38" t="n">
         <v>484.0067857142857</v>
@@ -14010,7 +14010,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -14031,10 +14031,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E39" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F39" t="n">
         <v>484.0067857142857</v>
@@ -14043,7 +14043,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E40" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F40" t="n">
         <v>484.0067857142857</v>
@@ -14076,7 +14076,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -14097,10 +14097,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E41" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F41" t="n">
         <v>484.0067857142857</v>
@@ -14109,7 +14109,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -14130,10 +14130,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E42" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F42" t="n">
         <v>484.0067857142857</v>
@@ -14142,7 +14142,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -14163,10 +14163,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6412.642857142857</v>
+        <v>6413</v>
       </c>
       <c r="E43" t="n">
-        <v>31.35714285714286</v>
+        <v>31</v>
       </c>
       <c r="F43" t="n">
         <v>484.0067857142857</v>
@@ -14175,7 +14175,7 @@
         <v>1299.182857142857</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5357142857142857</v>
+        <v>1</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week19.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week19.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
